--- a/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf75f8667508742c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f505fbc27a34708"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf41cbf7126264924"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0cf05a85c0e41ed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bfa521339e44950"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R724b39285b1c4c2d"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f505fbc27a34708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b48ac550a984d62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0cf05a85c0e41ed"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23bf7d48fa1b41ff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R724b39285b1c4c2d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re57680a8c2154a96"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b48ac550a984d62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R935341b9bc094980"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23bf7d48fa1b41ff"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2383168ad234447"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re57680a8c2154a96"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb207a6fcef60412d"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R935341b9bc094980"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e1ccd59d27c4042"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2383168ad234447"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R538511d3ce554cbc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb207a6fcef60412d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc322aeceae848db"/>
 </x:worksheet>
 </file>